--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H509"/>
+  <dimension ref="A1:H512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15708,6 +15708,96 @@
         <v>386.28</v>
       </c>
       <c r="H509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>402.43</v>
+      </c>
+      <c r="C510" t="n">
+        <v>372.36</v>
+      </c>
+      <c r="D510" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="E510" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="F510" t="n">
+        <v>382.88</v>
+      </c>
+      <c r="G510" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>404.15</v>
+      </c>
+      <c r="C511" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="D511" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="E511" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="F511" t="n">
+        <v>382.54</v>
+      </c>
+      <c r="G511" t="n">
+        <v>385.69</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>404.67</v>
+      </c>
+      <c r="C512" t="n">
+        <v>371.04</v>
+      </c>
+      <c r="D512" t="n">
+        <v>380.61</v>
+      </c>
+      <c r="E512" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="F512" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="G512" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="H512" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15724,7 +15814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B584"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21567,6 +21657,36 @@
       </c>
       <c r="B584" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -21735,28 +21855,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1770669096993215</v>
+        <v>0.1497840444017319</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005383133752736802</v>
+        <v>0.0038650947293426</v>
       </c>
       <c r="M2" t="n">
-        <v>15.03771308627951</v>
+        <v>15.09368977266669</v>
       </c>
       <c r="N2" t="n">
-        <v>350.7798136872337</v>
+        <v>352.3868181987641</v>
       </c>
       <c r="O2" t="n">
-        <v>18.72911673537313</v>
+        <v>18.77196894837524</v>
       </c>
       <c r="P2" t="n">
-        <v>424.2802743514619</v>
+        <v>424.5453211589049</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21813,28 +21933,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04913699678315462</v>
+        <v>0.04956815012011867</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01296635121026768</v>
+        <v>0.01334936931229636</v>
       </c>
       <c r="M3" t="n">
-        <v>2.803535538760194</v>
+        <v>2.79119712939303</v>
       </c>
       <c r="N3" t="n">
-        <v>11.12936855980236</v>
+        <v>11.06722157285305</v>
       </c>
       <c r="O3" t="n">
-        <v>3.336070826556648</v>
+        <v>3.326743388488665</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2201124086642</v>
+        <v>370.2159269448283</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21891,28 +22011,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07546189574176548</v>
+        <v>0.07441839883831312</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02018789545176303</v>
+        <v>0.01987479244251888</v>
       </c>
       <c r="M4" t="n">
-        <v>3.329173112544669</v>
+        <v>3.31515440106845</v>
       </c>
       <c r="N4" t="n">
-        <v>16.73579335634466</v>
+        <v>16.6444762034472</v>
       </c>
       <c r="O4" t="n">
-        <v>4.090940399999083</v>
+        <v>4.079764233806556</v>
       </c>
       <c r="P4" t="n">
-        <v>380.2941498873749</v>
+        <v>380.3042899922801</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21969,28 +22089,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07068559041356379</v>
+        <v>0.07093803766663934</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02874087934373282</v>
+        <v>0.0292851539653618</v>
       </c>
       <c r="M5" t="n">
-        <v>2.579397717267134</v>
+        <v>2.566866461970838</v>
       </c>
       <c r="N5" t="n">
-        <v>10.22435610471554</v>
+        <v>10.16560039043204</v>
       </c>
       <c r="O5" t="n">
-        <v>3.197554707071568</v>
+        <v>3.188353868445602</v>
       </c>
       <c r="P5" t="n">
-        <v>382.9000768483165</v>
+        <v>382.8976263710929</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22047,28 +22167,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02931812130858064</v>
+        <v>-0.02992326874056755</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005119649051265052</v>
+        <v>0.005396484560330816</v>
       </c>
       <c r="M6" t="n">
-        <v>2.478501469861746</v>
+        <v>2.467249277506665</v>
       </c>
       <c r="N6" t="n">
-        <v>10.11444520474706</v>
+        <v>10.05744460952288</v>
       </c>
       <c r="O6" t="n">
-        <v>3.180321556815766</v>
+        <v>3.171347443835645</v>
       </c>
       <c r="P6" t="n">
-        <v>383.8421475021993</v>
+        <v>383.8480279647046</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22125,28 +22245,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1049422728262314</v>
+        <v>-0.1028200850614398</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06648777520707594</v>
+        <v>0.06459405234143545</v>
       </c>
       <c r="M7" t="n">
-        <v>2.433546366710957</v>
+        <v>2.431035805359834</v>
       </c>
       <c r="N7" t="n">
-        <v>9.363069976522251</v>
+        <v>9.33026644070662</v>
       </c>
       <c r="O7" t="n">
-        <v>3.059913393630978</v>
+        <v>3.054548483934511</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4987133471057</v>
+        <v>386.4780967220219</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22184,7 +22304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H509"/>
+  <dimension ref="A1:H512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43565,6 +43685,132 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.98525025452264,173.44798582557672</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.98596344660762,173.44829741887258</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.98622433262633,173.44908273776934</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-34.98628744945214,173.44991649874834</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-34.98626339496445,173.45076691459195</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-34.986052337839595,173.45158148090275</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.985240126419505,173.44800009787028</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.98596351667556,173.44829734990623</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.98622672762848,173.44908176664805</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-34.98628997280365,173.4499163935302</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-34.98626641653618,173.45076754559096</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-34.98605285897639,173.45158165755586</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.98523706443452,173.44800441274901</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.98597269557631,173.448288315313</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.98623468245696,173.44907854113777</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-34.986296100943015,173.4499161380005</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-34.98627023793572,173.45076834361916</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-34.98605338011319,173.45158183420895</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H512"/>
+  <dimension ref="A1:H515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15798,6 +15798,96 @@
         <v>385.63</v>
       </c>
       <c r="H512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="C513" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="D513" t="n">
+        <v>378.61</v>
+      </c>
+      <c r="E513" t="n">
+        <v>382</v>
+      </c>
+      <c r="F513" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="G513" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="C514" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="D514" t="n">
+        <v>378.58</v>
+      </c>
+      <c r="E514" t="n">
+        <v>382.14</v>
+      </c>
+      <c r="F514" t="n">
+        <v>380.81</v>
+      </c>
+      <c r="G514" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>401.73</v>
+      </c>
+      <c r="C515" t="n">
+        <v>366.59</v>
+      </c>
+      <c r="D515" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="E515" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="F515" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="G515" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="H515" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15814,7 +15904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21687,6 +21777,36 @@
       </c>
       <c r="B587" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -21855,28 +21975,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1497840444017319</v>
+        <v>0.1195680148439163</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0038650947293426</v>
+        <v>0.002464636189258518</v>
       </c>
       <c r="M2" t="n">
-        <v>15.09368977266669</v>
+        <v>15.16743246095509</v>
       </c>
       <c r="N2" t="n">
-        <v>352.3868181987641</v>
+        <v>354.8935954869679</v>
       </c>
       <c r="O2" t="n">
-        <v>18.77196894837524</v>
+        <v>18.83861978720755</v>
       </c>
       <c r="P2" t="n">
-        <v>424.5453211589049</v>
+        <v>424.8401338147153</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21933,28 +22053,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04956815012011867</v>
+        <v>0.04537626441402407</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K3" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01334936931229636</v>
+        <v>0.01125566024884517</v>
       </c>
       <c r="M3" t="n">
-        <v>2.79119712939303</v>
+        <v>2.798377063402721</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06722157285305</v>
+        <v>11.09336133554834</v>
       </c>
       <c r="O3" t="n">
-        <v>3.326743388488665</v>
+        <v>3.330669802839714</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2159269448283</v>
+        <v>370.2568382139503</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22011,28 +22131,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07441839883831312</v>
+        <v>0.07019333016119281</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01987479244251888</v>
+        <v>0.01783966419651473</v>
       </c>
       <c r="M4" t="n">
-        <v>3.31515440106845</v>
+        <v>3.318036501922493</v>
       </c>
       <c r="N4" t="n">
-        <v>16.6444762034472</v>
+        <v>16.63719300101717</v>
       </c>
       <c r="O4" t="n">
-        <v>4.079764233806556</v>
+        <v>4.078871535243194</v>
       </c>
       <c r="P4" t="n">
-        <v>380.3042899922801</v>
+        <v>380.345520344657</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22089,28 +22209,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07093803766663934</v>
+        <v>0.0678955190698427</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K5" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0292851539653618</v>
+        <v>0.02709348570494519</v>
       </c>
       <c r="M5" t="n">
-        <v>2.566866461970838</v>
+        <v>2.568031905262698</v>
       </c>
       <c r="N5" t="n">
-        <v>10.16560039043204</v>
+        <v>10.15268937595988</v>
       </c>
       <c r="O5" t="n">
-        <v>3.188353868445602</v>
+        <v>3.186328510364221</v>
       </c>
       <c r="P5" t="n">
-        <v>382.8976263710929</v>
+        <v>382.9273153828449</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22167,28 +22287,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02992326874056755</v>
+        <v>-0.03262067162100643</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K6" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005396484560330816</v>
+        <v>0.006461095962335128</v>
       </c>
       <c r="M6" t="n">
-        <v>2.467249277506665</v>
+        <v>2.467395676930551</v>
       </c>
       <c r="N6" t="n">
-        <v>10.05744460952288</v>
+        <v>10.03591853842237</v>
       </c>
       <c r="O6" t="n">
-        <v>3.171347443835645</v>
+        <v>3.167951789156894</v>
       </c>
       <c r="P6" t="n">
-        <v>383.8480279647046</v>
+        <v>383.874352670362</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22245,28 +22365,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1028200850614398</v>
+        <v>-0.1026194275337913</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K7" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06459405234143545</v>
+        <v>0.06509554285843411</v>
       </c>
       <c r="M7" t="n">
-        <v>2.431035805359834</v>
+        <v>2.418080625022622</v>
       </c>
       <c r="N7" t="n">
-        <v>9.33026644070662</v>
+        <v>9.27615072979561</v>
       </c>
       <c r="O7" t="n">
-        <v>3.054548483934511</v>
+        <v>3.045677384391789</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4780967220219</v>
+        <v>386.476140940786</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22304,7 +22424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H512"/>
+  <dimension ref="A1:H515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43811,6 +43931,132 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.98526691878171,173.4479623426675</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.98599329554956,173.44826803919563</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.98625178961469,173.44907160455435</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-34.9863181802686,173.44991521734164</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-34.98628170213427,173.4507707377043</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-34.9860671033821,173.4515864860748</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.98526691878171,173.4479623426675</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.98599280507406,173.44826852196044</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.98625204622206,173.44907150050557</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-34.986316918592856,173.44991526995074</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-34.98628179100403,173.4507707562631</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-34.986067016525965,173.4515864566326</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.985254376424585,173.44798001708418</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.98600387580663,173.44825762526747</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.98625863247767,173.44906882992018</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-34.98632115421858,173.4499150933345</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-34.986289078324006,173.450772278085</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-34.98606996963443,173.45158745766722</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H515"/>
+  <dimension ref="A1:H517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15890,6 +15890,66 @@
       <c r="H515" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>409.25</v>
+      </c>
+      <c r="C516" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="D516" t="n">
+        <v>377.71</v>
+      </c>
+      <c r="E516" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="F516" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="G516" t="n">
+        <v>382.28</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>411.29</v>
+      </c>
+      <c r="C517" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="D517" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="E517" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="F517" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="G517" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B590"/>
+  <dimension ref="A1:B592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21807,6 +21867,26 @@
       </c>
       <c r="B590" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -21975,28 +22055,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1195680148439163</v>
+        <v>0.1068860230578372</v>
       </c>
       <c r="J2" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002464636189258518</v>
+        <v>0.001979884913167917</v>
       </c>
       <c r="M2" t="n">
-        <v>15.16743246095509</v>
+        <v>15.17779523906534</v>
       </c>
       <c r="N2" t="n">
-        <v>354.8935954869679</v>
+        <v>354.7292866895262</v>
       </c>
       <c r="O2" t="n">
-        <v>18.83861978720755</v>
+        <v>18.83425832597414</v>
       </c>
       <c r="P2" t="n">
-        <v>424.8401338147153</v>
+        <v>424.9646871792759</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22053,28 +22133,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04537626441402407</v>
+        <v>0.04122698490750865</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01125566024884517</v>
+        <v>0.009277588392369251</v>
       </c>
       <c r="M3" t="n">
-        <v>2.798377063402721</v>
+        <v>2.810522703677322</v>
       </c>
       <c r="N3" t="n">
-        <v>11.09336133554834</v>
+        <v>11.17984791657764</v>
       </c>
       <c r="O3" t="n">
-        <v>3.330669802839714</v>
+        <v>3.34362795726104</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2568382139503</v>
+        <v>370.2975897554414</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22131,28 +22211,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07019333016119281</v>
+        <v>0.06682584103543861</v>
       </c>
       <c r="J4" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01783966419651473</v>
+        <v>0.0162446173782389</v>
       </c>
       <c r="M4" t="n">
-        <v>3.318036501922493</v>
+        <v>3.322681621496454</v>
       </c>
       <c r="N4" t="n">
-        <v>16.63719300101717</v>
+        <v>16.65798098754814</v>
       </c>
       <c r="O4" t="n">
-        <v>4.078871535243194</v>
+        <v>4.081418991913001</v>
       </c>
       <c r="P4" t="n">
-        <v>380.345520344657</v>
+        <v>380.3785954167876</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22209,28 +22289,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0678955190698427</v>
+        <v>0.06552293771060179</v>
       </c>
       <c r="J5" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02709348570494519</v>
+        <v>0.02537884462370599</v>
       </c>
       <c r="M5" t="n">
-        <v>2.568031905262698</v>
+        <v>2.570572200578799</v>
       </c>
       <c r="N5" t="n">
-        <v>10.15268937595988</v>
+        <v>10.15562296635611</v>
       </c>
       <c r="O5" t="n">
-        <v>3.186328510364221</v>
+        <v>3.186788817345152</v>
       </c>
       <c r="P5" t="n">
-        <v>382.9273153828449</v>
+        <v>382.950618393267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22287,28 +22367,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03262067162100643</v>
+        <v>-0.03502005338547853</v>
       </c>
       <c r="J6" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006461095962335128</v>
+        <v>0.007467714970480266</v>
       </c>
       <c r="M6" t="n">
-        <v>2.467395676930551</v>
+        <v>2.470706548879708</v>
       </c>
       <c r="N6" t="n">
-        <v>10.03591853842237</v>
+        <v>10.04029277624397</v>
       </c>
       <c r="O6" t="n">
-        <v>3.167951789156894</v>
+        <v>3.168642102895809</v>
       </c>
       <c r="P6" t="n">
-        <v>383.874352670362</v>
+        <v>383.8979190382427</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22365,28 +22445,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1026194275337913</v>
+        <v>-0.1036622295127675</v>
       </c>
       <c r="J7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06509554285843411</v>
+        <v>0.06679003204640588</v>
       </c>
       <c r="M7" t="n">
-        <v>2.418080625022622</v>
+        <v>2.414198390030357</v>
       </c>
       <c r="N7" t="n">
-        <v>9.27615072979561</v>
+        <v>9.24835874996945</v>
       </c>
       <c r="O7" t="n">
-        <v>3.045677384391789</v>
+        <v>3.041111433336412</v>
       </c>
       <c r="P7" t="n">
-        <v>386.476140940786</v>
+        <v>386.4863828907991</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22424,7 +22504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H515"/>
+  <dimension ref="A1:H517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44057,6 +44137,90 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.98521009540624,173.4480424168595</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.986012213889374,173.44824941826258</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.98625948783555,173.44906848309088</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-34.986322596133725,173.44991503320983</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-34.98629094458888,173.45077266781993</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-34.98608247691725,173.4515916973441</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-34.98519808299684,173.44805934444653</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-34.98600864042541,173.4482529355506</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-34.98626308033857,173.44906702640773</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-34.98632439852764,173.44991495805397</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-34.98629334407227,173.4507731689077</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-34.98608230320501,173.4515916384597</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H517"/>
+  <dimension ref="A1:H520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15950,6 +15950,96 @@
       <c r="H517" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>413.19</v>
+      </c>
+      <c r="C518" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="D518" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="E518" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="F518" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="G518" t="n">
+        <v>382.2</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>413.19</v>
+      </c>
+      <c r="C519" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="D519" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="E519" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="F519" t="n">
+        <v>379.96</v>
+      </c>
+      <c r="G519" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>414.31</v>
+      </c>
+      <c r="C520" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="D520" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="E520" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="F520" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="G520" t="n">
+        <v>382.99</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B592"/>
+  <dimension ref="A1:B596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21887,6 +21977,46 @@
       </c>
       <c r="B592" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -22055,28 +22185,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1068860230578372</v>
+        <v>0.09176846514594353</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001979884913167917</v>
+        <v>0.001473293892851779</v>
       </c>
       <c r="M2" t="n">
-        <v>15.17779523906534</v>
+        <v>15.17216288740968</v>
       </c>
       <c r="N2" t="n">
-        <v>354.7292866895262</v>
+        <v>353.8337301841826</v>
       </c>
       <c r="O2" t="n">
-        <v>18.83425832597414</v>
+        <v>18.81046863276358</v>
       </c>
       <c r="P2" t="n">
-        <v>424.9646871792759</v>
+        <v>425.1138075669129</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22133,28 +22263,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04122698490750865</v>
+        <v>0.0362715093284305</v>
       </c>
       <c r="J3" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009277588392369251</v>
+        <v>0.007203328385281704</v>
       </c>
       <c r="M3" t="n">
-        <v>2.810522703677322</v>
+        <v>2.822054472370446</v>
       </c>
       <c r="N3" t="n">
-        <v>11.17984791657764</v>
+        <v>11.24088106681648</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34362795726104</v>
+        <v>3.352742320372457</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2975897554414</v>
+        <v>370.3464639934064</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22211,28 +22341,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06682584103543861</v>
+        <v>0.06175093764551074</v>
       </c>
       <c r="J4" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0162446173782389</v>
+        <v>0.01396416588645666</v>
       </c>
       <c r="M4" t="n">
-        <v>3.322681621496454</v>
+        <v>3.329846910165046</v>
       </c>
       <c r="N4" t="n">
-        <v>16.65798098754814</v>
+        <v>16.69193982064914</v>
       </c>
       <c r="O4" t="n">
-        <v>4.081418991913001</v>
+        <v>4.08557704867368</v>
       </c>
       <c r="P4" t="n">
-        <v>380.3785954167876</v>
+        <v>380.4286538425404</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22289,28 +22419,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06552293771060179</v>
+        <v>0.06216265712193147</v>
       </c>
       <c r="J5" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K5" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02537884462370599</v>
+        <v>0.02304757027729853</v>
       </c>
       <c r="M5" t="n">
-        <v>2.570572200578799</v>
+        <v>2.573627267535366</v>
       </c>
       <c r="N5" t="n">
-        <v>10.15562296635611</v>
+        <v>10.15428638745303</v>
       </c>
       <c r="O5" t="n">
-        <v>3.186788817345152</v>
+        <v>3.186579104220235</v>
       </c>
       <c r="P5" t="n">
-        <v>382.950618393267</v>
+        <v>382.9837618297535</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22367,28 +22497,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03502005338547853</v>
+        <v>-0.03811109523490364</v>
       </c>
       <c r="J6" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007467714970480266</v>
+        <v>0.008896582262755803</v>
       </c>
       <c r="M6" t="n">
-        <v>2.470706548879708</v>
+        <v>2.473103274229243</v>
       </c>
       <c r="N6" t="n">
-        <v>10.04029277624397</v>
+        <v>10.03091690696119</v>
       </c>
       <c r="O6" t="n">
-        <v>3.168642102895809</v>
+        <v>3.167162279858926</v>
       </c>
       <c r="P6" t="n">
-        <v>383.8979190382427</v>
+        <v>383.928406167011</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22445,28 +22575,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1036622295127675</v>
+        <v>-0.1047309196851421</v>
       </c>
       <c r="J7" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06679003204640588</v>
+        <v>0.06881337711181112</v>
       </c>
       <c r="M7" t="n">
-        <v>2.414198390030357</v>
+        <v>2.405799155159113</v>
       </c>
       <c r="N7" t="n">
-        <v>9.24835874996945</v>
+        <v>9.201437690463734</v>
       </c>
       <c r="O7" t="n">
-        <v>3.041111433336412</v>
+        <v>3.033387164617094</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4863828907991</v>
+        <v>386.4969203865234</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22504,7 +22634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H517"/>
+  <dimension ref="A1:H520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44221,6 +44351,132 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-34.98518689496635,173.44807511033193</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-34.98600646831981,173.4482550735098</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-34.986263508017494,173.44906685299307</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-34.98632484912612,173.449914939265</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-34.98629103345864,173.4507726863787</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-34.9860831717663,173.45159193288174</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-34.98518689496635,173.44807511033193</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-34.986004646553795,173.44825686663683</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-34.98626376462485,173.44906674894426</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-34.98632313685189,173.44991501066306</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-34.986289344933276,173.4507723337614</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-34.98607665755653,173.4515897247165</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-34.98518029991585,173.4480844039045</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-34.98599770982912,173.448263694312</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-34.98625965890711,173.44906841372503</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-34.986319351824655,173.44991516849035</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-34.98628534579427,173.45077149861518</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-34.986076310132,173.45158960694772</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H520"/>
+  <dimension ref="A1:H524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16038,6 +16038,126 @@
         <v>382.99</v>
       </c>
       <c r="H520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="C521" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="D521" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="E521" t="n">
+        <v>382.06</v>
+      </c>
+      <c r="F521" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="G521" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>405.82</v>
+      </c>
+      <c r="C522" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="D522" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="E522" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="F522" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="G522" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="C523" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="D523" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="E523" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="F523" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="G523" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>401.78</v>
+      </c>
+      <c r="C524" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="D524" t="n">
+        <v>377.04</v>
+      </c>
+      <c r="E524" t="n">
+        <v>382.2</v>
+      </c>
+      <c r="F524" t="n">
+        <v>381.64</v>
+      </c>
+      <c r="G524" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="H524" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16054,7 +16174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B596"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22017,6 +22137,46 @@
       </c>
       <c r="B596" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -22185,28 +22345,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09176846514594353</v>
+        <v>0.06048131195534327</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001473293892851779</v>
+        <v>0.0006438574367383376</v>
       </c>
       <c r="M2" t="n">
-        <v>15.17216288740968</v>
+        <v>15.22473097228184</v>
       </c>
       <c r="N2" t="n">
-        <v>353.8337301841826</v>
+        <v>354.9519467247545</v>
       </c>
       <c r="O2" t="n">
-        <v>18.81046863276358</v>
+        <v>18.84016843674054</v>
       </c>
       <c r="P2" t="n">
-        <v>425.1138075669129</v>
+        <v>425.4238226539375</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22263,28 +22423,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0362715093284305</v>
+        <v>0.03125567619011699</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007203328385281704</v>
+        <v>0.005398130941079438</v>
       </c>
       <c r="M3" t="n">
-        <v>2.822054472370446</v>
+        <v>2.828603752712397</v>
       </c>
       <c r="N3" t="n">
-        <v>11.24088106681648</v>
+        <v>11.25279066773291</v>
       </c>
       <c r="O3" t="n">
-        <v>3.352742320372457</v>
+        <v>3.354517948637763</v>
       </c>
       <c r="P3" t="n">
-        <v>370.3464639934064</v>
+        <v>370.3961551717065</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22341,28 +22501,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06175093764551074</v>
+        <v>0.05487634009882195</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01396416588645666</v>
+        <v>0.01111601450319455</v>
       </c>
       <c r="M4" t="n">
-        <v>3.329846910165046</v>
+        <v>3.340872438356608</v>
       </c>
       <c r="N4" t="n">
-        <v>16.69193982064914</v>
+        <v>16.7480058123562</v>
       </c>
       <c r="O4" t="n">
-        <v>4.08557704867368</v>
+        <v>4.092432749888042</v>
       </c>
       <c r="P4" t="n">
-        <v>380.4286538425404</v>
+        <v>380.4967690091904</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22419,28 +22579,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06216265712193147</v>
+        <v>0.05873764987351021</v>
       </c>
       <c r="J5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02304757027729853</v>
+        <v>0.02086460317313066</v>
       </c>
       <c r="M5" t="n">
-        <v>2.573627267535366</v>
+        <v>2.572259405138004</v>
       </c>
       <c r="N5" t="n">
-        <v>10.15428638745303</v>
+        <v>10.12190693984125</v>
       </c>
       <c r="O5" t="n">
-        <v>3.186579104220235</v>
+        <v>3.181494450700999</v>
       </c>
       <c r="P5" t="n">
-        <v>382.9837618297535</v>
+        <v>383.0176958656657</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22497,28 +22657,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03811109523490364</v>
+        <v>-0.04074019553958808</v>
       </c>
       <c r="J6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008896582262755803</v>
+        <v>0.0102880622934145</v>
       </c>
       <c r="M6" t="n">
-        <v>2.473103274229243</v>
+        <v>2.468340307699072</v>
       </c>
       <c r="N6" t="n">
-        <v>10.03091690696119</v>
+        <v>9.982010621889229</v>
       </c>
       <c r="O6" t="n">
-        <v>3.167162279858926</v>
+        <v>3.159432009379096</v>
       </c>
       <c r="P6" t="n">
-        <v>383.928406167011</v>
+        <v>383.9544500870259</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22575,28 +22735,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1047309196851421</v>
+        <v>-0.1038261885421081</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06881337711181112</v>
+        <v>0.06869984699961651</v>
       </c>
       <c r="M7" t="n">
-        <v>2.405799155159113</v>
+        <v>2.392671790849499</v>
       </c>
       <c r="N7" t="n">
-        <v>9.201437690463734</v>
+        <v>9.135752240604493</v>
       </c>
       <c r="O7" t="n">
-        <v>3.033387164617094</v>
+        <v>3.022540692960889</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4969203865234</v>
+        <v>386.4879520091087</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22634,7 +22794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H520"/>
+  <dimension ref="A1:H524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44477,6 +44637,174 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-34.985211861936854,173.44803992750803</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-34.98599777989703,173.4482636253456</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-34.98626068533657,173.44906799752985</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-34.98631763955043,173.44991523988838</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-34.98628392387818,173.45077120167437</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-34.98607049077122,173.4515876343204</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-34.98523029273639,173.4480139552682</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-34.985998410508394,173.4482630046479</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-34.98626094194392,173.44906789348104</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-34.986315116198945,173.44991534510658</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-34.986280635697206,173.45077051499865</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-34.98606553997173,173.45158595611534</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-34.98524189294925,173.447997608517</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-34.985995537723326,173.44826583227066</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-34.98627043641614,173.44906404367518</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-34.98631682847316,173.44991527370854</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-34.98628072456697,173.4507705335575</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-34.98606067602833,173.45158430735262</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-34.985254082003046,173.44798043197653</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-34.98599224453059,173.44826907369165</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-34.98626521873322,173.44906615933436</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-34.98631637787468,173.44991529249748</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-34.986274414814275,173.45076921588267</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-34.98606154458966,173.45158460177453</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H524"/>
+  <dimension ref="A1:H528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16158,6 +16158,126 @@
         <v>384.69</v>
       </c>
       <c r="H524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="C525" t="n">
+        <v>367.14</v>
+      </c>
+      <c r="D525" t="n">
+        <v>375.18</v>
+      </c>
+      <c r="E525" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="F525" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="G525" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="C526" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="D526" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="E526" t="n">
+        <v>380.81</v>
+      </c>
+      <c r="F526" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="G526" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>396.94</v>
+      </c>
+      <c r="C527" t="n">
+        <v>368.13</v>
+      </c>
+      <c r="D527" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="E527" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="F527" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="G527" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>394.98</v>
+      </c>
+      <c r="C528" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="D528" t="n">
+        <v>378.32</v>
+      </c>
+      <c r="E528" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="F528" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="G528" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="H528" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16174,7 +16294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22177,6 +22297,46 @@
       </c>
       <c r="B600" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -22345,28 +22505,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06048131195534327</v>
+        <v>0.01705036962978954</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006438574367383376</v>
+        <v>5.093534748845663e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>15.22473097228184</v>
+        <v>15.34697592675197</v>
       </c>
       <c r="N2" t="n">
-        <v>354.9519467247545</v>
+        <v>359.748417950704</v>
       </c>
       <c r="O2" t="n">
-        <v>18.84016843674054</v>
+        <v>18.96703503320179</v>
       </c>
       <c r="P2" t="n">
-        <v>425.4238226539375</v>
+        <v>425.8560700605503</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22423,28 +22583,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03125567619011699</v>
+        <v>0.02714582445549264</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005398130941079438</v>
+        <v>0.004108641443866468</v>
       </c>
       <c r="M3" t="n">
-        <v>2.828603752712397</v>
+        <v>2.830191873378888</v>
       </c>
       <c r="N3" t="n">
-        <v>11.25279066773291</v>
+        <v>11.25880986159691</v>
       </c>
       <c r="O3" t="n">
-        <v>3.354517948637763</v>
+        <v>3.355415005866921</v>
       </c>
       <c r="P3" t="n">
-        <v>370.3961551717065</v>
+        <v>370.4370420387437</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22501,28 +22661,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05487634009882195</v>
+        <v>0.04681622887129586</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01111601450319455</v>
+        <v>0.008112436292314618</v>
       </c>
       <c r="M4" t="n">
-        <v>3.340872438356608</v>
+        <v>3.358278805098591</v>
       </c>
       <c r="N4" t="n">
-        <v>16.7480058123562</v>
+        <v>16.89182960465902</v>
       </c>
       <c r="O4" t="n">
-        <v>4.092432749888042</v>
+        <v>4.109967105058023</v>
       </c>
       <c r="P4" t="n">
-        <v>380.4967690091904</v>
+        <v>380.5769735163282</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22579,28 +22739,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05873764987351021</v>
+        <v>0.05506601864174972</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02086460317313066</v>
+        <v>0.01854925297030663</v>
       </c>
       <c r="M5" t="n">
-        <v>2.572259405138004</v>
+        <v>2.572331347649226</v>
       </c>
       <c r="N5" t="n">
-        <v>10.12190693984125</v>
+        <v>10.1130494677879</v>
       </c>
       <c r="O5" t="n">
-        <v>3.181494450700999</v>
+        <v>3.180102115937144</v>
       </c>
       <c r="P5" t="n">
-        <v>383.0176958656657</v>
+        <v>383.0542238213946</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22657,28 +22817,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04074019553958808</v>
+        <v>-0.04234545001163195</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K6" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0102880622934145</v>
+        <v>0.01125803904932732</v>
       </c>
       <c r="M6" t="n">
-        <v>2.468340307699072</v>
+        <v>2.46071109743808</v>
       </c>
       <c r="N6" t="n">
-        <v>9.982010621889229</v>
+        <v>9.926734596933166</v>
       </c>
       <c r="O6" t="n">
-        <v>3.159432009379096</v>
+        <v>3.150672086544895</v>
       </c>
       <c r="P6" t="n">
-        <v>383.9544500870259</v>
+        <v>383.9704145787668</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22735,28 +22895,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1038261885421081</v>
+        <v>-0.1006838861156645</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06869984699961651</v>
+        <v>0.06552392259971462</v>
       </c>
       <c r="M7" t="n">
-        <v>2.392671790849499</v>
+        <v>2.39210039962747</v>
       </c>
       <c r="N7" t="n">
-        <v>9.135752240604493</v>
+        <v>9.112990753192301</v>
       </c>
       <c r="O7" t="n">
-        <v>3.022540692960889</v>
+        <v>3.01877305427094</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4879520091087</v>
+        <v>386.4566687604496</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22794,7 +22954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H524"/>
+  <dimension ref="A1:H528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44805,6 +44965,174 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-34.98527516258311,173.44795072567706</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-34.98600002207072,173.4482614184204</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-34.98628112838922,173.44905970830715</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-34.98633025630787,173.44991471379745</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-34.98628516805476,173.4507714614976</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-34.98606154458966,173.45158460177453</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-34.98531543942552,173.44789396834747</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-34.986004646553795,173.44825686663683</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-34.986284977499494,173.4490581475744</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-34.98632890451243,173.44991477016436</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-34.98628081343671,173.45077055211627</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-34.986054335530646,173.45158215807297</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-34.98528258200343,173.4479402703837</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-34.98599308534578,173.44826824609484</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-34.9862730024897,173.44906300318695</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-34.98631754943072,173.44991524364622</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-34.98627183759134,173.45076867767753</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-34.98604721332773,173.45157974381408</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-34.985294123322156,173.44792400659026</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-34.98597164455717,173.4482893498085</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-34.986254270152536,173.4490705987495</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-34.986298984773285,173.4499160177512</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-34.98625815164878,173.4507658196232</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-34.9860380065775,173.4515766229434</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
